--- a/docs/WB-SKU.xlsx
+++ b/docs/WB-SKU.xlsx
@@ -512,45 +512,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DE106AA</t>
+          <t>DE106AAAA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>167771171</v>
+        <v>362565043</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6913362823955</t>
+          <t>2043231560064</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DE106AAAA</t>
+          <t>DE107</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>362565043</v>
+        <v>65983485</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2043231560064</t>
+          <t>6913362825584</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DE107</t>
+          <t>DE107AA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65983485</v>
+        <v>167771171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6913362825584</t>
+          <t>6913362823955</t>
         </is>
       </c>
     </row>

--- a/docs/WB-SKU.xlsx
+++ b/docs/WB-SKU.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1202,58 +1202,43 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DE208AA</t>
+          <t>DE209</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>369137868</v>
+        <v>805033249</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2043337673552</t>
+          <t>6971663564649</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DE209</t>
+          <t>DE210</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>805033249</v>
+        <v>271980094</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>6971663564649</t>
+          <t>6971663562997</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DE210</t>
+          <t>DE310</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>271980094</v>
+        <v>313250836</v>
       </c>
       <c r="C54" t="inlineStr">
-        <is>
-          <t>6971663562997</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>DE310</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>313250836</v>
-      </c>
-      <c r="C55" t="inlineStr">
         <is>
           <t>6971663563000</t>
         </is>

--- a/docs/WB-SKU.xlsx
+++ b/docs/WB-SKU.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1172,73 +1172,58 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DE207AA</t>
+          <t>DE208</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>369120390</v>
+        <v>74753425</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2043337358510</t>
+          <t>4270002725232</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DE208</t>
+          <t>DE209</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>74753425</v>
+        <v>805033249</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4270002725232</t>
+          <t>6971663564649</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DE209</t>
+          <t>DE210</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>805033249</v>
+        <v>271980094</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>6971663564649</t>
+          <t>6971663562997</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DE210</t>
+          <t>DE310</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>271980094</v>
+        <v>313250836</v>
       </c>
       <c r="C53" t="inlineStr">
-        <is>
-          <t>6971663562997</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>DE310</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>313250836</v>
-      </c>
-      <c r="C54" t="inlineStr">
         <is>
           <t>6971663563000</t>
         </is>

--- a/docs/WB-SKU.xlsx
+++ b/docs/WB-SKU.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1229,6 +1229,21 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Напиши описание для Вальбериса. </t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>998663744</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SB63191484234</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/WB-SKU.xlsx
+++ b/docs/WB-SKU.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -737,508 +737,523 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DE118 KINDER 1+</t>
+          <t>DE117AA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>76666340</v>
+        <v>1000956242</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6913362821371</t>
+          <t>2050915546399</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DE118AAAA</t>
+          <t>DE118 KINDER 1+</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>362564713</v>
+        <v>76666340</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2043231857201</t>
+          <t>6913362821371</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DE118DE118-светло-персиковый</t>
+          <t>DE118AAAA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>180681762</v>
+        <v>362564713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2038745406113</t>
+          <t>2043231857201</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DE119 GROSSE</t>
+          <t>DE118DE118-светло-персиковый</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>145687295</v>
+        <v>180681762</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6913362829803</t>
+          <t>2038745406113</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DE119AA</t>
+          <t>DE119 GROSSE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>368186401</v>
+        <v>145687295</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2043323196850</t>
+          <t>6913362829803</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DE120</t>
+          <t>DE119AA</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65981631</v>
+        <v>368186401</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6913362825935</t>
+          <t>2043323196850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DE120AA</t>
+          <t>DE120</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>167774509</v>
+        <v>65981631</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6913362820848</t>
+          <t>6913362825935</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DE120AAAA</t>
+          <t>DE120AA</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>169621984</v>
+        <v>167774509</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6913362825942</t>
+          <t>6913362820848</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DE121AAAA</t>
+          <t>DE120AAAA</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>363381681</v>
+        <v>169621984</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2043245779612</t>
+          <t>6913362825942</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DE122AAAA</t>
+          <t>DE121AAAA</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65981822</v>
+        <v>363381681</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6913362825126</t>
+          <t>2043245779612</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DE123</t>
+          <t>DE122AAAA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65982721</v>
+        <v>65981822</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6913362820107</t>
+          <t>6913362825126</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DE123AA</t>
+          <t>DE123</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>167774311</v>
+        <v>65982721</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6913362829858</t>
+          <t>6913362820107</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DE123AAAA</t>
+          <t>DE123AA</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>179218772</v>
+        <v>167774311</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6913362824297</t>
+          <t>6913362829858</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DE124DE124</t>
+          <t>DE123AAAA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>67823602</v>
+        <v>179218772</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6913362827298</t>
+          <t>6913362824297</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DE125</t>
+          <t>DE124DE124</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>79106526</v>
+        <v>67823602</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6913362829094</t>
+          <t>6913362827298</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DE126</t>
+          <t>DE125</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>79106904</v>
+        <v>79106526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6913362827670</t>
+          <t>6913362829094</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DE130</t>
+          <t>DE126</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>79105837</v>
+        <v>79106904</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6913362829087</t>
+          <t>6913362827670</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DE201</t>
+          <t>DE130</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>74734089</v>
+        <v>79105837</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4270001210609</t>
+          <t>6913362829087</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DE201AA</t>
+          <t>DE201</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>198719422</v>
+        <v>74734089</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OZN1381946886</t>
+          <t>4270001210609</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DE202</t>
+          <t>DE201AA</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>74736092</v>
+        <v>198719422</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4270001210623</t>
+          <t>OZN1381946886</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DE202AA</t>
+          <t>DE202</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>231270026</v>
+        <v>74736092</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OZN1359408834</t>
+          <t>4270001210623</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DE203</t>
+          <t>DE202AA</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>74737960</v>
+        <v>231270026</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4270001210630</t>
+          <t>OZN1359408834</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DE203AA</t>
+          <t>DE203</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>64892684</v>
+        <v>74737960</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OZN1359365941</t>
+          <t>4270001210630</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DE204DE204</t>
+          <t>DE203AA</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>74740869</v>
+        <v>64892684</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4270002725294</t>
+          <t>OZN1359365941</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DE205</t>
+          <t>DE204DE204</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>74744320</v>
+        <v>74740869</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4270001210647</t>
+          <t>4270002725294</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DE205AA</t>
+          <t>DE205</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>342270493</v>
+        <v>74744320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OZN1359459315</t>
+          <t>4270001210647</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DE206</t>
+          <t>DE205AA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>74750650</v>
+        <v>342270493</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>4270001210654</t>
+          <t>OZN1359459315</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DE206AA</t>
+          <t>DE206</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>255312431</v>
+        <v>74750650</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2041001965767</t>
+          <t>4270001210654</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DE207</t>
+          <t>DE206AA</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>74752505</v>
+        <v>255312431</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>6971663561860</t>
+          <t>2041001965767</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DE208</t>
+          <t>DE207</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>74753425</v>
+        <v>74752505</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4270002725232</t>
+          <t>6971663561860</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DE209</t>
+          <t>DE208</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>805033249</v>
+        <v>74753425</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>6971663564649</t>
+          <t>4270002725232</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DE210</t>
+          <t>DE209</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>271980094</v>
+        <v>805033249</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>6971663562997</t>
+          <t>6971663564649</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DE310</t>
+          <t>DE210</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>313250836</v>
+        <v>271980094</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>6971663563000</t>
+          <t>6971663562997</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>DE310</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>313250836</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>6971663563000</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Напиши описание для Вальбериса. </t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B55" t="n">
         <v>998663744</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>SB63191484234</t>
         </is>

--- a/docs/WB-SKU.xlsx
+++ b/docs/WB-SKU.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -752,508 +752,523 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DE118 KINDER 1+</t>
+          <t>DE117AA</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>76666340</v>
+        <v>1000956242</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6913362821371</t>
+          <t>SB36622362327</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DE118AAAA</t>
+          <t>DE118 KINDER 1+</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>362564713</v>
+        <v>76666340</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2043231857201</t>
+          <t>6913362821371</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DE118DE118-светло-персиковый</t>
+          <t>DE118AAAA</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>180681762</v>
+        <v>362564713</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2038745406113</t>
+          <t>2043231857201</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DE119 GROSSE</t>
+          <t>DE118DE118-светло-персиковый</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>145687295</v>
+        <v>180681762</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6913362829803</t>
+          <t>2038745406113</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DE119AA</t>
+          <t>DE119 GROSSE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>368186401</v>
+        <v>145687295</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2043323196850</t>
+          <t>6913362829803</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DE120</t>
+          <t>DE119AA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65981631</v>
+        <v>368186401</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6913362825935</t>
+          <t>2043323196850</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DE120AA</t>
+          <t>DE120</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>167774509</v>
+        <v>65981631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6913362820848</t>
+          <t>6913362825935</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DE120AAAA</t>
+          <t>DE120AA</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>169621984</v>
+        <v>167774509</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6913362825942</t>
+          <t>6913362820848</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DE121AAAA</t>
+          <t>DE120AAAA</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>363381681</v>
+        <v>169621984</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2043245779612</t>
+          <t>6913362825942</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DE122AAAA</t>
+          <t>DE121AAAA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65981822</v>
+        <v>363381681</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6913362825126</t>
+          <t>2043245779612</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DE123</t>
+          <t>DE122AAAA</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65982721</v>
+        <v>65981822</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6913362820107</t>
+          <t>6913362825126</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DE123AA</t>
+          <t>DE123</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>167774311</v>
+        <v>65982721</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6913362829858</t>
+          <t>6913362820107</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DE123AAAA</t>
+          <t>DE123AA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>179218772</v>
+        <v>167774311</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6913362824297</t>
+          <t>6913362829858</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DE124DE124</t>
+          <t>DE123AAAA</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>67823602</v>
+        <v>179218772</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6913362827298</t>
+          <t>6913362824297</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DE125</t>
+          <t>DE124DE124</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>79106526</v>
+        <v>67823602</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6913362829094</t>
+          <t>6913362827298</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DE126</t>
+          <t>DE125</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>79106904</v>
+        <v>79106526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6913362827670</t>
+          <t>6913362829094</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DE130</t>
+          <t>DE126</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>79105837</v>
+        <v>79106904</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6913362829087</t>
+          <t>6913362827670</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DE201</t>
+          <t>DE130</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>74734089</v>
+        <v>79105837</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4270001210609</t>
+          <t>6913362829087</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DE201AA</t>
+          <t>DE201</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>198719422</v>
+        <v>74734089</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OZN1381946886</t>
+          <t>4270001210609</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DE202</t>
+          <t>DE201AA</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>74736092</v>
+        <v>198719422</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4270001210623</t>
+          <t>OZN1381946886</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DE202AA</t>
+          <t>DE202</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>231270026</v>
+        <v>74736092</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OZN1359408834</t>
+          <t>4270001210623</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DE203</t>
+          <t>DE202AA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>74737960</v>
+        <v>231270026</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4270001210630</t>
+          <t>OZN1359408834</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DE203AA</t>
+          <t>DE203</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>64892684</v>
+        <v>74737960</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OZN1359365941</t>
+          <t>4270001210630</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DE204DE204</t>
+          <t>DE203AA</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>74740869</v>
+        <v>64892684</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4270002725294</t>
+          <t>OZN1359365941</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DE205</t>
+          <t>DE204DE204</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>74744320</v>
+        <v>74740869</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4270001210647</t>
+          <t>4270002725294</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DE205AA</t>
+          <t>DE205</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>342270493</v>
+        <v>74744320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OZN1359459315</t>
+          <t>4270001210647</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DE206</t>
+          <t>DE205AA</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>74750650</v>
+        <v>342270493</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4270001210654</t>
+          <t>OZN1359459315</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DE206AA</t>
+          <t>DE206</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>255312431</v>
+        <v>74750650</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2041001965767</t>
+          <t>4270001210654</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DE207</t>
+          <t>DE206AA</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>74752505</v>
+        <v>255312431</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>6971663561860</t>
+          <t>2041001965767</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DE208</t>
+          <t>DE207</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>74753425</v>
+        <v>74752505</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4270002725232</t>
+          <t>6971663561860</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DE209</t>
+          <t>DE208</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>805033249</v>
+        <v>74753425</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>6971663564649</t>
+          <t>4270002725232</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DE210</t>
+          <t>DE209</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>271980094</v>
+        <v>805033249</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>6971663562997</t>
+          <t>6971663564649</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DE310</t>
+          <t>DE210</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>313250836</v>
+        <v>271980094</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>6971663563000</t>
+          <t>6971663562997</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>DE310</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>313250836</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6971663563000</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Напиши описание для Вальбериса. </t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B56" t="n">
         <v>998663744</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>SB63191484234</t>
         </is>

--- a/docs/WB-SKU.xlsx
+++ b/docs/WB-SKU.xlsx
@@ -512,45 +512,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DE106AAAA</t>
+          <t>DE106AA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>362565043</v>
+        <v>167771171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2043231560064</t>
+          <t>6913362823955</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DE107</t>
+          <t>DE106AAAA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65983485</v>
+        <v>362565043</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6913362825584</t>
+          <t>2043231560064</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DE107AA</t>
+          <t>DE107</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>167771171</v>
+        <v>65983485</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6913362823955</t>
+          <t>6913362825584</t>
         </is>
       </c>
     </row>

--- a/docs/WB-SKU.xlsx
+++ b/docs/WB-SKU.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -745,530 +745,515 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2050915546399</t>
+          <t>SB36622362327</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DE117AA</t>
+          <t>DE118 KINDER 1+</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1000956242</v>
+        <v>76666340</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SB36622362327</t>
+          <t>6913362821371</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DE118 KINDER 1+</t>
+          <t>DE118AAAA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>76666340</v>
+        <v>362564713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6913362821371</t>
+          <t>2043231857201</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DE118AAAA</t>
+          <t>DE118DE118-светло-персиковый</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>362564713</v>
+        <v>180681762</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2043231857201</t>
+          <t>2038745406113</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DE118DE118-светло-персиковый</t>
+          <t>DE119 GROSSE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>180681762</v>
+        <v>145687295</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2038745406113</t>
+          <t>6913362829803</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DE119 GROSSE</t>
+          <t>DE119AA</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>145687295</v>
+        <v>368186401</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6913362829803</t>
+          <t>2043323196850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DE119AA</t>
+          <t>DE120</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>368186401</v>
+        <v>65981631</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2043323196850</t>
+          <t>6913362825935</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DE120</t>
+          <t>DE120AA</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65981631</v>
+        <v>167774509</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6913362825935</t>
+          <t>6913362820848</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DE120AA</t>
+          <t>DE120AAAA</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>167774509</v>
+        <v>169621984</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6913362820848</t>
+          <t>6913362825942</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DE120AAAA</t>
+          <t>DE121AAAA</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>169621984</v>
+        <v>363381681</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6913362825942</t>
+          <t>2043245779612</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DE121AAAA</t>
+          <t>DE122AAAA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>363381681</v>
+        <v>65981822</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2043245779612</t>
+          <t>6913362825126</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DE122AAAA</t>
+          <t>DE123</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65981822</v>
+        <v>65982721</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6913362825126</t>
+          <t>6913362820107</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DE123</t>
+          <t>DE123AA</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65982721</v>
+        <v>167774311</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6913362820107</t>
+          <t>6913362829858</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DE123AA</t>
+          <t>DE123AAAA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>167774311</v>
+        <v>179218772</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6913362829858</t>
+          <t>6913362824297</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DE123AAAA</t>
+          <t>DE124DE124</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>179218772</v>
+        <v>67823602</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6913362824297</t>
+          <t>6913362827298</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DE124DE124</t>
+          <t>DE125</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>67823602</v>
+        <v>79106526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6913362827298</t>
+          <t>6913362829094</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DE125</t>
+          <t>DE126</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>79106526</v>
+        <v>79106904</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6913362829094</t>
+          <t>6913362827670</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DE126</t>
+          <t>DE130</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>79106904</v>
+        <v>79105837</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6913362827670</t>
+          <t>6913362829087</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DE130</t>
+          <t>DE201</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>79105837</v>
+        <v>74734089</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6913362829087</t>
+          <t>4270001210609</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DE201</t>
+          <t>DE201AA</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>74734089</v>
+        <v>198719422</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4270001210609</t>
+          <t>OZN1381946886</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DE201AA</t>
+          <t>DE202</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>198719422</v>
+        <v>74736092</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OZN1381946886</t>
+          <t>4270001210623</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DE202</t>
+          <t>DE202AA</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>74736092</v>
+        <v>231270026</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4270001210623</t>
+          <t>OZN1359408834</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DE202AA</t>
+          <t>DE203</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>231270026</v>
+        <v>74737960</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OZN1359408834</t>
+          <t>4270001210630</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DE203</t>
+          <t>DE203AA</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>74737960</v>
+        <v>64892684</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4270001210630</t>
+          <t>OZN1359365941</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DE203AA</t>
+          <t>DE204DE204</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64892684</v>
+        <v>74740869</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OZN1359365941</t>
+          <t>4270002725294</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DE204DE204</t>
+          <t>DE205</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>74740869</v>
+        <v>74744320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4270002725294</t>
+          <t>4270001210647</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DE205</t>
+          <t>DE205AA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>74744320</v>
+        <v>342270493</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>4270001210647</t>
+          <t>OZN1359459315</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DE205AA</t>
+          <t>DE206</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>342270493</v>
+        <v>74750650</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OZN1359459315</t>
+          <t>4270001210654</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DE206</t>
+          <t>DE206AA</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>74750650</v>
+        <v>255312431</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>4270001210654</t>
+          <t>2041001965767</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DE206AA</t>
+          <t>DE207</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>255312431</v>
+        <v>74752505</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2041001965767</t>
+          <t>6971663561860</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DE207</t>
+          <t>DE208</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>74752505</v>
+        <v>74753425</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>6971663561860</t>
+          <t>4270002725232</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DE208</t>
+          <t>DE209</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>74753425</v>
+        <v>805033249</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>4270002725232</t>
+          <t>6971663564649</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DE209</t>
+          <t>DE210</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>805033249</v>
+        <v>271980094</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>6971663564649</t>
+          <t>6971663562997</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DE210</t>
+          <t>DE310</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>271980094</v>
+        <v>313250836</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>6971663562997</t>
+          <t>6971663563000</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DE310</t>
+          <t xml:space="preserve">Напиши описание для Вальбериса. </t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>313250836</v>
+        <v>998663744</v>
       </c>
       <c r="C55" t="inlineStr">
-        <is>
-          <t>6971663563000</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Напиши описание для Вальбериса. </t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>998663744</v>
-      </c>
-      <c r="C56" t="inlineStr">
         <is>
           <t>SB63191484234</t>
         </is>

--- a/docs/WB-SKU.xlsx
+++ b/docs/WB-SKU.xlsx
@@ -752,7 +752,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DE118 KINDER 1+</t>
+          <t>DE118</t>
         </is>
       </c>
       <c r="B22" t="n">
